--- a/frontend/public/ejemplos/planificacion_nia/RQ-005_informe_anterior.xlsx
+++ b/frontend/public/ejemplos/planificacion_nia/RQ-005_informe_anterior.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -443,6 +443,11 @@
           <t>Fuente o referencia</t>
         </is>
       </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Efecto en el enfoque</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -466,6 +471,7 @@
           <t>Informe 2024 · Nota 1</t>
         </is>
       </c>
+      <c r="F2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -489,56 +495,211 @@
           <t>Informe 2024 · Nota 1</t>
         </is>
       </c>
+      <c r="F3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Opinión del año anterior</t>
+          <t>RUC</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Opinión</t>
+          <t>Identificación</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Con salvedades (por el asunto de jubilación patronal)</t>
+          <t>0999999999001 (ficticio)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Informe 2024 · Opinión</t>
-        </is>
-      </c>
+          <t>Informe 2024 · Nota 1</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>País y moneda funcional</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Identificación</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ecuador · dólar de los Estados Unidos (USD)</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Informe 2024 · Nota 2</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Opinión del año anterior</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Opinión</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Con salvedades (por el asunto de jubilación patronal)</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Informe 2024 · Opinión</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t>Jubilación patronal</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>Salvedad</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>La provisión no se ajustó al cálculo actuarial al cierre; el pasivo estaría subestimado.</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>18500.00</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>Informe 2024 · Fundamento de la opinión</t>
         </is>
       </c>
+      <c r="F7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Proveedor principal vinculado</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Entendimiento</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>El 60 % de las compras se hace a un proveedor del exterior vinculado al accionista mayoritario.</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Informe 2024 · Nota 20 (partes relacionadas)</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Riesgo de partes relacionadas y precios de transferencia: confirmar saldos y evaluar los términos (NIA 550).</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Ventas concentradas en el último trimestre</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Entendimiento</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Cerca del 40 % de las ventas del año se factura entre octubre y diciembre (temporada navideña).</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Informe 2024 · Nota 18 (ingresos)</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Riesgo de corte de ingresos al cierre: ampliar la prueba de corte y revisar las notas de crédito posteriores (NIA 240).</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Constitución e historia</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Contexto</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Sociedad anónima constituida en 1998; distribuye productos de consumo masivo en la Costa y la Sierra.</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Informe 2024 · Nota 1</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Sistema de información</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Contexto</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>ERP integrado para ventas, inventarios y contabilidad, con cierres mensuales.</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Carta de control interno 2024</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -571,7 +732,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Una fila por dato o asunto del informe: concepto, tipo (Identificación, Opinión, Salvedad, Énfasis, Empresa en marcha, Asunto clave, Otro asunto), detalle, importe si lo tiene y la fuente (párrafo o nota).</t>
+          <t>Una fila por dato o asunto del informe: concepto, tipo (Identificación, Entendimiento, Contexto, Opinión, Salvedad, Énfasis, Empresa en marcha, Asunto clave, Otro asunto), detalle, importe si lo tiene y la fuente (párrafo o nota).</t>
         </is>
       </c>
     </row>

--- a/frontend/public/ejemplos/planificacion_nia/RQ-005_informe_anterior.xlsx
+++ b/frontend/public/ejemplos/planificacion_nia/RQ-005_informe_anterior.xlsx
@@ -732,7 +732,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Una fila por dato o asunto del informe: concepto, tipo (Identificación, Entendimiento, Contexto, Opinión, Salvedad, Énfasis, Empresa en marcha, Asunto clave, Otro asunto), detalle, importe si lo tiene y la fuente (párrafo o nota).</t>
+          <t>Una fila por dato o asunto del informe: concepto, tipo (Identificación, Entendimiento, Contexto, Opinión, Salvedad, Desfavorable, Abstención, Énfasis, Empresa en marcha, Asunto clave, Otro asunto), detalle, importe si lo tiene y la fuente (párrafo o nota).</t>
         </is>
       </c>
     </row>
